--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,8 +778,16 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600553</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91580</v>
+        <v>91582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91582</v>
+        <v>91584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,6 +1157,9 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öster-Hasslingen, Jmt</t>
@@ -1215,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135769287</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135769288</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135769289</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135769290</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135769292</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135769293</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>135769294</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135769295</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>135769296</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135769297</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135769298</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135769299</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>135769300</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135769301</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135769302</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135769303</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>135769304</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135769305</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135769306</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>135769307</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135769308</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>135769309</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>135769312</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135769313</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135769314</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135769315</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135769316</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135769318</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>135769319</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135769320</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135769322</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>135769323</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135769324</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135769325</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769326</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135769327</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135769328</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135769329</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>135769330</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135769331</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135769332</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>135769333</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135769335</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135769336</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135769337</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135769338</v>
       </c>
       <c r="B54" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135769339</v>
       </c>
       <c r="B55" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>135769341</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>135769342</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135769343</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>135769344</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>135769345</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>135769347</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135769348</v>
       </c>
       <c r="B62" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135769349</v>
       </c>
       <c r="B63" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>135769350</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>135769351</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>135769352</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135769354</v>
       </c>
       <c r="B67" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>135769355</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135769356</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>135769357</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>135769359</v>
       </c>
       <c r="B71" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>135769360</v>
       </c>
       <c r="B72" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135769361</v>
       </c>
       <c r="B73" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>135769362</v>
       </c>
       <c r="B74" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>135769363</v>
       </c>
       <c r="B75" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>135769364</v>
       </c>
       <c r="B76" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135769365</v>
       </c>
       <c r="B77" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>135769366</v>
       </c>
       <c r="B78" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>135769367</v>
       </c>
       <c r="B79" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>135769368</v>
       </c>
       <c r="B80" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769369</v>
       </c>
       <c r="B81" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>135769370</v>
       </c>
       <c r="B82" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>135769371</v>
       </c>
       <c r="B83" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>135769372</v>
       </c>
       <c r="B84" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135769373</v>
       </c>
       <c r="B85" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135769374</v>
       </c>
       <c r="B86" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135769375</v>
       </c>
       <c r="B87" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135769287</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135769288</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135769289</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135769290</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135769292</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135769293</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>135769294</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135769295</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>135769296</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135769297</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135769298</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135769299</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>135769300</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135769301</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135769302</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135769303</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>135769304</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135769305</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135769306</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>135769307</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135769308</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>135769309</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>135769312</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135769313</v>
       </c>
       <c r="B32" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135769314</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135769315</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135769316</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135769318</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>135769319</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135769320</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135769322</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>135769323</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135769324</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135769325</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769326</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135769327</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135769328</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135769329</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>135769330</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135769331</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135769332</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>135769333</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135769335</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135769336</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135769337</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135769338</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135769339</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>135769341</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>135769342</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135769343</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>135769344</v>
       </c>
       <c r="B59" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>135769345</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>135769347</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135769348</v>
       </c>
       <c r="B62" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135769349</v>
       </c>
       <c r="B63" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>135769350</v>
       </c>
       <c r="B64" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>135769351</v>
       </c>
       <c r="B65" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>135769352</v>
       </c>
       <c r="B66" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135769354</v>
       </c>
       <c r="B67" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>135769355</v>
       </c>
       <c r="B68" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135769356</v>
       </c>
       <c r="B69" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>135769357</v>
       </c>
       <c r="B70" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>135769359</v>
       </c>
       <c r="B71" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>135769360</v>
       </c>
       <c r="B72" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135769361</v>
       </c>
       <c r="B73" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>135769362</v>
       </c>
       <c r="B74" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>135769363</v>
       </c>
       <c r="B75" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>135769364</v>
       </c>
       <c r="B76" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135769365</v>
       </c>
       <c r="B77" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>135769366</v>
       </c>
       <c r="B78" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>135769367</v>
       </c>
       <c r="B79" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>135769368</v>
       </c>
       <c r="B80" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769369</v>
       </c>
       <c r="B81" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>135769370</v>
       </c>
       <c r="B82" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>135769371</v>
       </c>
       <c r="B83" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>135769372</v>
       </c>
       <c r="B84" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135769373</v>
       </c>
       <c r="B85" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135769374</v>
       </c>
       <c r="B86" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135769375</v>
       </c>
       <c r="B87" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135769287</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135769288</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135769289</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135769290</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135769292</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135769293</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>135769294</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135769295</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>135769296</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135769297</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135769298</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135769299</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>135769300</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135769301</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135769302</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135769303</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>135769304</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135769305</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135769306</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>135769307</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135769308</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>135769309</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>135769312</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135769313</v>
       </c>
       <c r="B32" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135769314</v>
       </c>
       <c r="B33" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135769315</v>
       </c>
       <c r="B34" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135769316</v>
       </c>
       <c r="B35" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135769318</v>
       </c>
       <c r="B36" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>135769319</v>
       </c>
       <c r="B37" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135769320</v>
       </c>
       <c r="B38" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135769322</v>
       </c>
       <c r="B39" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>135769323</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135769324</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135769325</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769326</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135769327</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135769328</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135769329</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>135769330</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135769331</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135769332</v>
       </c>
       <c r="B49" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>135769333</v>
       </c>
       <c r="B50" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135769335</v>
       </c>
       <c r="B51" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135769336</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135769337</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135769338</v>
       </c>
       <c r="B54" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135769339</v>
       </c>
       <c r="B55" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>135769341</v>
       </c>
       <c r="B56" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>135769342</v>
       </c>
       <c r="B57" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135769343</v>
       </c>
       <c r="B58" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>135769344</v>
       </c>
       <c r="B59" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>135769345</v>
       </c>
       <c r="B60" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>135769347</v>
       </c>
       <c r="B61" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135769348</v>
       </c>
       <c r="B62" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135769349</v>
       </c>
       <c r="B63" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>135769350</v>
       </c>
       <c r="B64" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>135769351</v>
       </c>
       <c r="B65" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>135769352</v>
       </c>
       <c r="B66" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135769354</v>
       </c>
       <c r="B67" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>135769355</v>
       </c>
       <c r="B68" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135769356</v>
       </c>
       <c r="B69" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>135769357</v>
       </c>
       <c r="B70" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>135769359</v>
       </c>
       <c r="B71" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>135769360</v>
       </c>
       <c r="B72" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135769361</v>
       </c>
       <c r="B73" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>135769362</v>
       </c>
       <c r="B74" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>135769363</v>
       </c>
       <c r="B75" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>135769364</v>
       </c>
       <c r="B76" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135769365</v>
       </c>
       <c r="B77" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>135769366</v>
       </c>
       <c r="B78" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>135769367</v>
       </c>
       <c r="B79" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>135769368</v>
       </c>
       <c r="B80" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769369</v>
       </c>
       <c r="B81" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>135769370</v>
       </c>
       <c r="B82" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>135769371</v>
       </c>
       <c r="B83" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>135769372</v>
       </c>
       <c r="B84" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135769373</v>
       </c>
       <c r="B85" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135769374</v>
       </c>
       <c r="B86" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135769375</v>
       </c>
       <c r="B87" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135769287</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135769288</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135769289</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135769290</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135769292</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135769293</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>135769294</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135769295</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>135769296</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135769297</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135769298</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135769299</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>135769300</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135769301</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135769302</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135769303</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>135769304</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135769305</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135769306</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>135769307</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135769308</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>135769309</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>135769312</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135769313</v>
       </c>
       <c r="B32" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135769314</v>
       </c>
       <c r="B33" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135769315</v>
       </c>
       <c r="B34" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135769316</v>
       </c>
       <c r="B35" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135769318</v>
       </c>
       <c r="B36" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>135769319</v>
       </c>
       <c r="B37" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135769320</v>
       </c>
       <c r="B38" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135769322</v>
       </c>
       <c r="B39" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>135769323</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135769324</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135769325</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769326</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135769327</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135769328</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135769329</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>135769330</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135769331</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135769332</v>
       </c>
       <c r="B49" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>135769333</v>
       </c>
       <c r="B50" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135769335</v>
       </c>
       <c r="B51" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135769336</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135769337</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135769338</v>
       </c>
       <c r="B54" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135769339</v>
       </c>
       <c r="B55" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>135769341</v>
       </c>
       <c r="B56" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>135769342</v>
       </c>
       <c r="B57" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135769343</v>
       </c>
       <c r="B58" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>135769344</v>
       </c>
       <c r="B59" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>135769345</v>
       </c>
       <c r="B60" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>135769347</v>
       </c>
       <c r="B61" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135769348</v>
       </c>
       <c r="B62" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135769349</v>
       </c>
       <c r="B63" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>135769350</v>
       </c>
       <c r="B64" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>135769351</v>
       </c>
       <c r="B65" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>135769352</v>
       </c>
       <c r="B66" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135769354</v>
       </c>
       <c r="B67" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>135769355</v>
       </c>
       <c r="B68" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135769356</v>
       </c>
       <c r="B69" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>135769357</v>
       </c>
       <c r="B70" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>135769359</v>
       </c>
       <c r="B71" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>135769360</v>
       </c>
       <c r="B72" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135769361</v>
       </c>
       <c r="B73" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>135769362</v>
       </c>
       <c r="B74" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>135769363</v>
       </c>
       <c r="B75" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>135769364</v>
       </c>
       <c r="B76" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135769365</v>
       </c>
       <c r="B77" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>135769366</v>
       </c>
       <c r="B78" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>135769367</v>
       </c>
       <c r="B79" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>135769368</v>
       </c>
       <c r="B80" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769369</v>
       </c>
       <c r="B81" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>135769370</v>
       </c>
       <c r="B82" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>135769371</v>
       </c>
       <c r="B83" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>135769372</v>
       </c>
       <c r="B84" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135769373</v>
       </c>
       <c r="B85" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135769374</v>
       </c>
       <c r="B86" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135769375</v>
       </c>
       <c r="B87" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769317</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769353</v>
       </c>
       <c r="B3" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135769321</v>
       </c>
       <c r="B4" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135769311</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>135769346</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135769287</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135769288</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135769289</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135769290</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>135769292</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135769293</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>135769294</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135769295</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>135769296</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135769297</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135769298</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135769299</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>135769300</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135769301</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135769302</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135769303</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>135769304</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135769305</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135769306</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>135769307</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135769308</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>135769309</v>
       </c>
       <c r="B30" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>135769312</v>
       </c>
       <c r="B31" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135769313</v>
       </c>
       <c r="B32" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135769314</v>
       </c>
       <c r="B33" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135769315</v>
       </c>
       <c r="B34" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135769316</v>
       </c>
       <c r="B35" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135769318</v>
       </c>
       <c r="B36" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>135769319</v>
       </c>
       <c r="B37" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135769320</v>
       </c>
       <c r="B38" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>135769322</v>
       </c>
       <c r="B39" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>135769323</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135769324</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>135769325</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769326</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135769327</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135769328</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>135769329</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>135769330</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135769331</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135769332</v>
       </c>
       <c r="B49" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>135769333</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135769335</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>135769336</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135769337</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135769338</v>
       </c>
       <c r="B54" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135769339</v>
       </c>
       <c r="B55" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>135769341</v>
       </c>
       <c r="B56" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>135769342</v>
       </c>
       <c r="B57" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>135769343</v>
       </c>
       <c r="B58" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>135769344</v>
       </c>
       <c r="B59" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>135769345</v>
       </c>
       <c r="B60" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>135769347</v>
       </c>
       <c r="B61" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135769348</v>
       </c>
       <c r="B62" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>135769349</v>
       </c>
       <c r="B63" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>135769350</v>
       </c>
       <c r="B64" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>135769351</v>
       </c>
       <c r="B65" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>135769352</v>
       </c>
       <c r="B66" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135769354</v>
       </c>
       <c r="B67" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>135769355</v>
       </c>
       <c r="B68" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135769356</v>
       </c>
       <c r="B69" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>135769357</v>
       </c>
       <c r="B70" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>135769359</v>
       </c>
       <c r="B71" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>135769360</v>
       </c>
       <c r="B72" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135769361</v>
       </c>
       <c r="B73" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>135769362</v>
       </c>
       <c r="B74" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>135769363</v>
       </c>
       <c r="B75" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>135769364</v>
       </c>
       <c r="B76" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135769365</v>
       </c>
       <c r="B77" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>135769366</v>
       </c>
       <c r="B78" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>135769367</v>
       </c>
       <c r="B79" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>135769368</v>
       </c>
       <c r="B80" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769369</v>
       </c>
       <c r="B81" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>135769370</v>
       </c>
       <c r="B82" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>135769371</v>
       </c>
       <c r="B83" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>135769372</v>
       </c>
       <c r="B84" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>135769373</v>
       </c>
       <c r="B85" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135769374</v>
       </c>
       <c r="B86" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135769375</v>
       </c>
       <c r="B87" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30922-2026 artfynd.xlsx
+++ b/artfynd/A 30922-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>135769358</v>
       </c>
       <c r="B6" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
